--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.81156589835056</v>
+        <v>7.444379458481966</v>
       </c>
       <c r="D2" t="n">
-        <v>45.70550757361603</v>
+        <v>7.427144980712606</v>
       </c>
       <c r="E2" t="n">
-        <v>6.048463051142965</v>
+        <v>0.9828752458107318</v>
       </c>
       <c r="F2" t="n">
-        <v>5.871562358654548</v>
+        <v>0.954128883281364</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.45986245425993</v>
+        <v>6.737227648817238</v>
       </c>
       <c r="D3" t="n">
-        <v>41.09532999282047</v>
+        <v>6.677991123833326</v>
       </c>
       <c r="E3" t="n">
-        <v>6.048463051142965</v>
+        <v>0.9828752458107318</v>
       </c>
       <c r="F3" t="n">
-        <v>5.871562358654548</v>
+        <v>0.954128883281364</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.22414766000096</v>
+        <v>5.398923994750156</v>
       </c>
       <c r="D4" t="n">
-        <v>33.58457593225927</v>
+        <v>5.457493588992132</v>
       </c>
       <c r="E4" t="n">
-        <v>6.048463051142965</v>
+        <v>0.9828752458107318</v>
       </c>
       <c r="F4" t="n">
-        <v>5.871562358654548</v>
+        <v>0.954128883281364</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.4820824785649</v>
+        <v>4.628338402766797</v>
       </c>
       <c r="D5" t="n">
-        <v>28.71609623531458</v>
+        <v>4.66636563823862</v>
       </c>
       <c r="E5" t="n">
-        <v>6.048463051142965</v>
+        <v>0.9828752458107318</v>
       </c>
       <c r="F5" t="n">
-        <v>5.871562358654548</v>
+        <v>0.954128883281364</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.10431507824575</v>
+        <v>6.841951200214934</v>
       </c>
       <c r="D6" t="n">
-        <v>41.93587772041412</v>
+        <v>6.814580129567295</v>
       </c>
       <c r="E6" t="n">
-        <v>6.048463051142965</v>
+        <v>0.9828752458107318</v>
       </c>
       <c r="F6" t="n">
-        <v>5.871562358654548</v>
+        <v>0.954128883281364</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.66630706547974</v>
+        <v>6.933274898140457</v>
       </c>
       <c r="D7" t="n">
-        <v>42.71517953481577</v>
+        <v>6.941216674407563</v>
       </c>
       <c r="E7" t="n">
-        <v>6.048463051142965</v>
+        <v>0.9828752458107318</v>
       </c>
       <c r="F7" t="n">
-        <v>5.871562358654548</v>
+        <v>0.954128883281364</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
